--- a/clients.xlsx
+++ b/clients.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,183 @@
           <t>⚠️ Ошибка генерации.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[Kwork] Telegram-бот для механиков в Google Таблицы</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://kwork.ru/projects/3127892</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>⚠️ Ошибка генерации.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-20 15:07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[Kwork] Telegram-бот магазин + админка</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://kwork.ru/projects/3127931</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>⚠️ Ошибка генерации.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-20 15:18</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[Kwork] Web-приложение с подключением к API (WHOOP) и ЛК</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://kwork.ru/projects/3127951</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>⚠️ Ошибка генерации.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-20 15:19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[Kwork] Починить телеграм бота</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://kwork.ru/projects/3127944</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>⚠️ Ошибка генерации.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-20 15:20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[Kwork] Скрипт для преобразования текста в речь и наоборот</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://kwork.ru/projects/3089940</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>⚠️ Ошибка генерации.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-20 15:51</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[FL] Запрос на разработку Telegram-бота с интеграцией ИИ (без перехода на внешние сервисы)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.fl.ru/projects/5495603/zapros-na-razrabotku-telegram-bota-s-integratsiey-ii-bez-perehoda-na-vneshnie-servisyi.html</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>⚠️ Ошибка генерации.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-20 15:57</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[Kwork] Парсер</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://kwork.ru/projects/3127992</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>⚠️ Ошибка генерации.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-20 15:58</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[Kwork] Разработка telegram mini app для изучения английского</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://kwork.ru/projects/3127997</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>⚠️ Ошибка генерации.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
